--- a/reviews/REVIEWED_FrancescaHongWI_20260101_20260107_20260803_autoPush.xlsx
+++ b/reviews/REVIEWED_FrancescaHongWI_20260101_20260107_20260803_autoPush.xlsx
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr"/>
     </row>
